--- a/artfynd/A 64892-2023 artfynd.xlsx
+++ b/artfynd/A 64892-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121540996</v>
       </c>
       <c r="B2" t="n">
-        <v>91154</v>
+        <v>91159</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121540816</v>
+        <v>121541052</v>
       </c>
       <c r="B3" t="n">
-        <v>78608</v>
+        <v>56559</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,37 +797,54 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2, Dlr</t>
+          <t>9, Fjällgrycken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530491</v>
+        <v>530653</v>
       </c>
       <c r="R3" t="n">
-        <v>6739260</v>
+        <v>6739025</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,28 +874,17 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121540928</v>
+        <v>121540923</v>
       </c>
       <c r="B4" t="n">
         <v>78608</v>
@@ -936,14 +942,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>6, Dlr</t>
+          <t>5, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530586</v>
+        <v>530450</v>
       </c>
       <c r="R4" t="n">
-        <v>6739209</v>
+        <v>6739221</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,7 +1009,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121540923</v>
+        <v>121540928</v>
       </c>
       <c r="B5" t="n">
         <v>78608</v>
@@ -1042,14 +1048,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>5, Dlr</t>
+          <t>6, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530450</v>
+        <v>530586</v>
       </c>
       <c r="R5" t="n">
-        <v>6739221</v>
+        <v>6739209</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121541052</v>
+        <v>121541039</v>
       </c>
       <c r="B6" t="n">
-        <v>56559</v>
+        <v>90719</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,54 +1131,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>9, Fjällgrycken, Dlr</t>
+          <t>8, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530653</v>
+        <v>530628</v>
       </c>
       <c r="R6" t="n">
-        <v>6739025</v>
+        <v>6739034</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,6 +1202,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1231,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121541039</v>
+        <v>121540816</v>
       </c>
       <c r="B7" t="n">
-        <v>90714</v>
+        <v>78608</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,21 +1237,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,14 +1260,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>8, Dlr</t>
+          <t>2, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530628</v>
+        <v>530491</v>
       </c>
       <c r="R7" t="n">
-        <v>6739034</v>
+        <v>6739260</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,9 +1297,19 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 64892-2023 artfynd.xlsx
+++ b/artfynd/A 64892-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121540996</v>
+        <v>121540816</v>
       </c>
       <c r="B2" t="n">
-        <v>91159</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>7, Dlr</t>
+          <t>2, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530649</v>
+        <v>530491</v>
       </c>
       <c r="R2" t="n">
-        <v>6739106</v>
+        <v>6739260</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,9 +751,19 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121541052</v>
+        <v>121541039</v>
       </c>
       <c r="B3" t="n">
-        <v>56559</v>
+        <v>90720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,54 +807,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>9, Fjällgrycken, Dlr</t>
+          <t>8, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530653</v>
+        <v>530628</v>
       </c>
       <c r="R3" t="n">
-        <v>6739025</v>
+        <v>6739034</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,6 +878,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121540923</v>
+        <v>121540996</v>
       </c>
       <c r="B4" t="n">
-        <v>78608</v>
+        <v>91160</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,14 +936,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>5, Dlr</t>
+          <t>7, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530450</v>
+        <v>530649</v>
       </c>
       <c r="R4" t="n">
-        <v>6739221</v>
+        <v>6739106</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,7 +1006,7 @@
         <v>121540928</v>
       </c>
       <c r="B5" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1115,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121541039</v>
+        <v>121541052</v>
       </c>
       <c r="B6" t="n">
-        <v>90719</v>
+        <v>56560</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,37 +1125,54 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>8, Dlr</t>
+          <t>9, Fjällgrycken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530628</v>
+        <v>530653</v>
       </c>
       <c r="R6" t="n">
-        <v>6739034</v>
+        <v>6739025</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1213,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1221,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121540816</v>
+        <v>121540923</v>
       </c>
       <c r="B7" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,14 +1270,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2, Dlr</t>
+          <t>5, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530491</v>
+        <v>530450</v>
       </c>
       <c r="R7" t="n">
-        <v>6739260</v>
+        <v>6739221</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,19 +1307,9 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 64892-2023 artfynd.xlsx
+++ b/artfynd/A 64892-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121540816</v>
+        <v>121540928</v>
       </c>
       <c r="B2" t="n">
         <v>78609</v>
@@ -714,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2, Dlr</t>
+          <t>6, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530491</v>
+        <v>530586</v>
       </c>
       <c r="R2" t="n">
-        <v>6739260</v>
+        <v>6739209</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +751,9 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121541039</v>
+        <v>121540816</v>
       </c>
       <c r="B3" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,14 +820,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>8, Dlr</t>
+          <t>2, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530628</v>
+        <v>530491</v>
       </c>
       <c r="R3" t="n">
-        <v>6739034</v>
+        <v>6739260</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,9 +857,19 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121540928</v>
+        <v>121541052</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>56560</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,37 +1019,54 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>6, Dlr</t>
+          <t>9, Fjällgrycken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530586</v>
+        <v>530653</v>
       </c>
       <c r="R5" t="n">
-        <v>6739209</v>
+        <v>6739025</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1107,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1109,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121541052</v>
+        <v>121541039</v>
       </c>
       <c r="B6" t="n">
-        <v>56560</v>
+        <v>90720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,54 +1141,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>9, Fjällgrycken, Dlr</t>
+          <t>8, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530653</v>
+        <v>530628</v>
       </c>
       <c r="R6" t="n">
-        <v>6739025</v>
+        <v>6739034</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,6 +1212,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64892-2023 artfynd.xlsx
+++ b/artfynd/A 64892-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121540928</v>
+        <v>121540996</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>91160</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>6, Dlr</t>
+          <t>7, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530586</v>
+        <v>530649</v>
       </c>
       <c r="R2" t="n">
-        <v>6739209</v>
+        <v>6739106</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121540816</v>
+        <v>121540923</v>
       </c>
       <c r="B3" t="n">
         <v>78609</v>
@@ -820,14 +820,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2, Dlr</t>
+          <t>5, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530491</v>
+        <v>530450</v>
       </c>
       <c r="R3" t="n">
-        <v>6739260</v>
+        <v>6739221</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,19 +857,9 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121540996</v>
+        <v>121540816</v>
       </c>
       <c r="B4" t="n">
-        <v>91160</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,14 +926,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>7, Dlr</t>
+          <t>2, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530649</v>
+        <v>530491</v>
       </c>
       <c r="R4" t="n">
-        <v>6739106</v>
+        <v>6739260</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,9 +963,19 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121541052</v>
+        <v>121541039</v>
       </c>
       <c r="B5" t="n">
-        <v>56560</v>
+        <v>90720</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,54 +1019,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>9, Fjällgrycken, Dlr</t>
+          <t>8, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530653</v>
+        <v>530628</v>
       </c>
       <c r="R5" t="n">
-        <v>6739025</v>
+        <v>6739034</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,6 +1090,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1125,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121541039</v>
+        <v>121541052</v>
       </c>
       <c r="B6" t="n">
-        <v>90720</v>
+        <v>56560</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,37 +1125,54 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>8, Dlr</t>
+          <t>9, Fjällgrycken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530628</v>
+        <v>530653</v>
       </c>
       <c r="R6" t="n">
-        <v>6739034</v>
+        <v>6739025</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1213,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1231,7 +1231,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121540923</v>
+        <v>121540928</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1270,14 +1270,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>5, Dlr</t>
+          <t>6, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530450</v>
+        <v>530586</v>
       </c>
       <c r="R7" t="n">
-        <v>6739221</v>
+        <v>6739209</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 64892-2023 artfynd.xlsx
+++ b/artfynd/A 64892-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121540996</v>
+        <v>121540928</v>
       </c>
       <c r="B2" t="n">
-        <v>91160</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>7, Dlr</t>
+          <t>6, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530649</v>
+        <v>530586</v>
       </c>
       <c r="R2" t="n">
-        <v>6739106</v>
+        <v>6739209</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121540923</v>
+        <v>121541039</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,14 +820,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>5, Dlr</t>
+          <t>8, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530450</v>
+        <v>530628</v>
       </c>
       <c r="R3" t="n">
-        <v>6739221</v>
+        <v>6739034</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121541039</v>
+        <v>121541052</v>
       </c>
       <c r="B5" t="n">
-        <v>90720</v>
+        <v>56560</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,37 +1019,54 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>8, Dlr</t>
+          <t>9, Fjällgrycken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530628</v>
+        <v>530653</v>
       </c>
       <c r="R5" t="n">
-        <v>6739034</v>
+        <v>6739025</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1107,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1109,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121541052</v>
+        <v>121540923</v>
       </c>
       <c r="B6" t="n">
-        <v>56560</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,54 +1141,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>9, Fjällgrycken, Dlr</t>
+          <t>5, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530653</v>
+        <v>530450</v>
       </c>
       <c r="R6" t="n">
-        <v>6739025</v>
+        <v>6739221</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,6 +1212,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1231,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121540928</v>
+        <v>121540996</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>91160</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,25 +1243,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,14 +1270,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>6, Dlr</t>
+          <t>7, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530586</v>
+        <v>530649</v>
       </c>
       <c r="R7" t="n">
-        <v>6739209</v>
+        <v>6739106</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,6 +1334,564 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121635412</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>530656</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6739100</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121645979</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90720</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>10, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>530657</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6739025</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Linn Grejs</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Linn Grejs, Cecilia Rastad, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121643705</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ol-Larsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>530609</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6739158</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Cecilia Rastad, Linn Grejs</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121645997</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90720</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>11, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>530662</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6739074</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Linn Grejs</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Linn Grejs, Cecilia Rastad, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121635669</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>530668</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6739052</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64892-2023 artfynd.xlsx
+++ b/artfynd/A 64892-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121541039</v>
+        <v>121540816</v>
       </c>
       <c r="B3" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,14 +820,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>8, Dlr</t>
+          <t>2, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530628</v>
+        <v>530491</v>
       </c>
       <c r="R3" t="n">
-        <v>6739034</v>
+        <v>6739260</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,9 +857,19 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121540816</v>
+        <v>121540923</v>
       </c>
       <c r="B4" t="n">
         <v>78609</v>
@@ -926,14 +936,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2, Dlr</t>
+          <t>5, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530491</v>
+        <v>530450</v>
       </c>
       <c r="R4" t="n">
-        <v>6739260</v>
+        <v>6739221</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,19 +973,9 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121541052</v>
+        <v>121635412</v>
       </c>
       <c r="B5" t="n">
-        <v>56560</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,16 +1019,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1036,40 +1036,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>9, Fjällgrycken, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530653</v>
+        <v>530656</v>
       </c>
       <c r="R5" t="n">
-        <v>6739025</v>
+        <v>6739100</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,12 +1081,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,22 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121540923</v>
+        <v>121645979</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1164,17 +1162,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>5, Dlr</t>
+          <t>10, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530450</v>
+        <v>530657</v>
       </c>
       <c r="R6" t="n">
-        <v>6739221</v>
+        <v>6739025</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,12 +1196,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,17 +1222,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Linn Grejs, Cecilia Rastad, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121540996</v>
+        <v>121643705</v>
       </c>
       <c r="B7" t="n">
-        <v>91160</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,25 +1241,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,17 +1268,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>7, Dlr</t>
+          <t>Ol-Larsbo, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530649</v>
+        <v>530609</v>
       </c>
       <c r="R7" t="n">
-        <v>6739106</v>
+        <v>6739158</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1304,12 +1302,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,19 +1323,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Lars-Erik Nilsson, Cecilia Rastad, Linn Grejs</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121635412</v>
+        <v>121635669</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1375,7 +1373,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1385,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530656</v>
+        <v>530668</v>
       </c>
       <c r="R8" t="n">
-        <v>6739100</v>
+        <v>6739052</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1420,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1430,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,7 +1455,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121645979</v>
+        <v>121645997</v>
       </c>
       <c r="B9" t="n">
         <v>90720</v>
@@ -1496,14 +1494,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>10, Dlr</t>
+          <t>11, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530657</v>
+        <v>530662</v>
       </c>
       <c r="R9" t="n">
-        <v>6739025</v>
+        <v>6739074</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1563,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121643705</v>
+        <v>121631634</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>8435</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,44 +1573,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ol-Larsbo, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530609</v>
+        <v>530482</v>
       </c>
       <c r="R10" t="n">
-        <v>6739158</v>
+        <v>6739197</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1639,40 +1634,49 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Cecilia Rastad, Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121645997</v>
+        <v>121540996</v>
       </c>
       <c r="B11" t="n">
-        <v>90720</v>
+        <v>91160</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1681,25 +1685,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,17 +1712,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>11, Dlr</t>
+          <t>7, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530662</v>
+        <v>530649</v>
       </c>
       <c r="R11" t="n">
-        <v>6739074</v>
+        <v>6739106</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1742,12 +1746,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,17 +1772,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linn Grejs, Cecilia Rastad, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121635669</v>
+        <v>121631841</v>
       </c>
       <c r="B12" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1791,42 +1795,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>530668</v>
+        <v>530484</v>
       </c>
       <c r="R12" t="n">
-        <v>6739052</v>
+        <v>6739192</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1858,7 +1854,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1868,7 +1864,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,6 +1888,1452 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121632076</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8435</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>530487</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6739191</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121632944</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>530510</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6739257</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121656060</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>14, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>530597</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6739160</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Linn Grejs</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Linn Grejs</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121632920</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>530531</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6739254</v>
+      </c>
+      <c r="S16" t="n">
+        <v>28</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121632008</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>530493</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6739190</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121541052</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56560</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>9, Fjällgrycken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>530653</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6739025</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Linn Grejs</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Linn Grejs</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121647286</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Fjällgrycksån,, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>530655</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6739083</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lars-Erik Nilsson, Linn Grejs</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121631713</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>530489</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6739205</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121656035</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>12, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>530558</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6739302</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Linn Grejs</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Linn Grejs</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121633817</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>530605</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6739161</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121656049</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>13, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>530570</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6739299</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Linn Grejs</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Linn Grejs</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121633302</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>530588</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6739210</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121541039</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90720</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>8, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>530628</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6739034</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Linn Grejs</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Linn Grejs</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64892-2023 artfynd.xlsx
+++ b/artfynd/A 64892-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121540928</v>
+        <v>121540816</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -714,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>6, Dlr</t>
+          <t>2, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530586</v>
+        <v>530491</v>
       </c>
       <c r="R2" t="n">
-        <v>6739209</v>
+        <v>6739260</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,9 +751,19 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121540816</v>
+        <v>121540923</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,14 +830,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2, Dlr</t>
+          <t>5, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530491</v>
+        <v>530450</v>
       </c>
       <c r="R3" t="n">
-        <v>6739260</v>
+        <v>6739221</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,19 +867,9 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121540923</v>
+        <v>121540928</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,14 +936,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>5, Dlr</t>
+          <t>6, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530450</v>
+        <v>530586</v>
       </c>
       <c r="R4" t="n">
-        <v>6739221</v>
+        <v>6739209</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121635412</v>
+        <v>121645997</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>90728</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,45 +1019,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>11, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530656</v>
+        <v>530662</v>
       </c>
       <c r="R5" t="n">
-        <v>6739100</v>
+        <v>6739074</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,49 +1079,40 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs, Cecilia Rastad, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121645979</v>
+        <v>121635669</v>
       </c>
       <c r="B6" t="n">
-        <v>90720</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,40 +1125,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>10, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530657</v>
+        <v>530668</v>
       </c>
       <c r="R6" t="n">
-        <v>6739025</v>
+        <v>6739052</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,40 +1190,49 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linn Grejs, Cecilia Rastad, Lars-Erik Nilsson</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121643705</v>
+        <v>121645979</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>90728</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,21 +1245,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1268,14 +1268,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ol-Larsbo, Dlr</t>
+          <t>10, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530609</v>
+        <v>530657</v>
       </c>
       <c r="R7" t="n">
-        <v>6739158</v>
+        <v>6739025</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1323,22 +1323,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Cecilia Rastad, Linn Grejs</t>
+          <t>Linn Grejs, Cecilia Rastad, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121635669</v>
+        <v>121635412</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530668</v>
+        <v>530656</v>
       </c>
       <c r="R8" t="n">
-        <v>6739052</v>
+        <v>6739100</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121645997</v>
+        <v>121643705</v>
       </c>
       <c r="B9" t="n">
-        <v>90720</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,14 +1494,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>11, Dlr</t>
+          <t>Ol-Larsbo, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530662</v>
+        <v>530609</v>
       </c>
       <c r="R9" t="n">
-        <v>6739074</v>
+        <v>6739158</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1549,22 +1549,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linn Grejs, Cecilia Rastad, Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Cecilia Rastad, Linn Grejs</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121631634</v>
+        <v>121540996</v>
       </c>
       <c r="B10" t="n">
-        <v>8435</v>
+        <v>91168</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,41 +1573,44 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>7, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530482</v>
+        <v>530649</v>
       </c>
       <c r="R10" t="n">
-        <v>6739197</v>
+        <v>6739106</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,22 +1634,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:02</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:02</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,28 +1648,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121540996</v>
+        <v>121632920</v>
       </c>
       <c r="B11" t="n">
-        <v>91160</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1685,44 +1679,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>7, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530649</v>
+        <v>530531</v>
       </c>
       <c r="R11" t="n">
-        <v>6739106</v>
+        <v>6739254</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1746,12 +1737,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,29 +1761,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121631841</v>
+        <v>121631713</v>
       </c>
       <c r="B12" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>530484</v>
+        <v>530489</v>
       </c>
       <c r="R12" t="n">
-        <v>6739192</v>
+        <v>6739205</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1891,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121632076</v>
+        <v>121541052</v>
       </c>
       <c r="B13" t="n">
-        <v>8435</v>
+        <v>56561</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1903,41 +1903,61 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>9, Fjällgrycken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530487</v>
+        <v>530653</v>
       </c>
       <c r="R13" t="n">
-        <v>6739191</v>
+        <v>6739025</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1961,22 +1981,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1991,22 +2001,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121632944</v>
+        <v>121656049</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>57373</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,37 +2029,41 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>13, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530510</v>
+        <v>530570</v>
       </c>
       <c r="R14" t="n">
-        <v>6739257</v>
+        <v>6739299</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2076,19 +2090,9 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2103,22 +2107,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121656060</v>
+        <v>121633302</v>
       </c>
       <c r="B15" t="n">
-        <v>57372</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2131,41 +2135,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>14, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530597</v>
+        <v>530588</v>
       </c>
       <c r="R15" t="n">
-        <v>6739160</v>
+        <v>6739210</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2192,9 +2192,19 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2209,22 +2219,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121632920</v>
+        <v>121633817</v>
       </c>
       <c r="B16" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2261,13 +2271,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>530531</v>
+        <v>530605</v>
       </c>
       <c r="R16" t="n">
-        <v>6739254</v>
+        <v>6739161</v>
       </c>
       <c r="S16" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2296,7 +2306,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2306,7 +2316,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2336,7 +2346,7 @@
         <v>121632008</v>
       </c>
       <c r="B17" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2445,10 +2455,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121541052</v>
+        <v>121632944</v>
       </c>
       <c r="B18" t="n">
-        <v>56560</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2461,57 +2471,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>9, Fjällgrycken, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>530653</v>
+        <v>530510</v>
       </c>
       <c r="R18" t="n">
-        <v>6739025</v>
+        <v>6739257</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2535,12 +2525,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2555,22 +2555,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121647286</v>
+        <v>121632076</v>
       </c>
       <c r="B19" t="n">
-        <v>78609</v>
+        <v>8436</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2579,41 +2579,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fjällgrycksån,, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>530655</v>
+        <v>530487</v>
       </c>
       <c r="R19" t="n">
-        <v>6739083</v>
+        <v>6739191</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2645,7 +2642,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2655,7 +2652,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2664,7 +2661,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2676,17 +2672,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lars-Erik Nilsson, Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121631713</v>
+        <v>121656060</v>
       </c>
       <c r="B20" t="n">
-        <v>78609</v>
+        <v>57373</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2699,37 +2695,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>14, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530489</v>
+        <v>530597</v>
       </c>
       <c r="R20" t="n">
-        <v>6739205</v>
+        <v>6739160</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2756,19 +2756,9 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:08</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,22 +2773,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121656035</v>
+        <v>121647286</v>
       </c>
       <c r="B21" t="n">
-        <v>57372</v>
+        <v>78616</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2811,41 +2801,40 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>12, Dlr</t>
+          <t>Fjällgrycksån,, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530558</v>
+        <v>530655</v>
       </c>
       <c r="R21" t="n">
-        <v>6739302</v>
+        <v>6739083</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2872,39 +2861,50 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Lars-Erik Nilsson, Linn Grejs</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121633817</v>
+        <v>121656035</v>
       </c>
       <c r="B22" t="n">
-        <v>78609</v>
+        <v>57373</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2917,37 +2917,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>12, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530605</v>
+        <v>530558</v>
       </c>
       <c r="R22" t="n">
-        <v>6739161</v>
+        <v>6739302</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2974,19 +2978,9 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3001,22 +2995,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121656049</v>
+        <v>121631634</v>
       </c>
       <c r="B23" t="n">
-        <v>57372</v>
+        <v>8436</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3025,45 +3019,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>13, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530570</v>
+        <v>530482</v>
       </c>
       <c r="R23" t="n">
-        <v>6739299</v>
+        <v>6739197</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3090,9 +3080,19 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3107,22 +3107,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121633302</v>
+        <v>121631841</v>
       </c>
       <c r="B24" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530588</v>
+        <v>530484</v>
       </c>
       <c r="R24" t="n">
-        <v>6739210</v>
+        <v>6739192</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3234,7 +3234,7 @@
         <v>121541039</v>
       </c>
       <c r="B25" t="n">
-        <v>90720</v>
+        <v>90728</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 64892-2023 artfynd.xlsx
+++ b/artfynd/A 64892-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121540816</v>
+        <v>121540928</v>
       </c>
       <c r="B2" t="n">
         <v>78616</v>
@@ -714,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2, Dlr</t>
+          <t>6, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530491</v>
+        <v>530586</v>
       </c>
       <c r="R2" t="n">
-        <v>6739260</v>
+        <v>6739209</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +751,9 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121540923</v>
+        <v>121540816</v>
       </c>
       <c r="B3" t="n">
         <v>78616</v>
@@ -830,14 +820,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>5, Dlr</t>
+          <t>2, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530450</v>
+        <v>530491</v>
       </c>
       <c r="R3" t="n">
-        <v>6739221</v>
+        <v>6739260</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,9 +857,19 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121540928</v>
+        <v>121540923</v>
       </c>
       <c r="B4" t="n">
         <v>78616</v>
@@ -936,14 +936,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>6, Dlr</t>
+          <t>5, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530586</v>
+        <v>530450</v>
       </c>
       <c r="R4" t="n">
-        <v>6739209</v>
+        <v>6739221</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121635669</v>
+        <v>121643705</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,45 +1019,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>Ol-Larsbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530668</v>
+        <v>530609</v>
       </c>
       <c r="R5" t="n">
-        <v>6739052</v>
+        <v>6739158</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,49 +1079,40 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Cecilia Rastad, Linn Grejs</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121645979</v>
+        <v>121635669</v>
       </c>
       <c r="B6" t="n">
-        <v>90728</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,40 +1125,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>10, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530657</v>
+        <v>530668</v>
       </c>
       <c r="R6" t="n">
-        <v>6739025</v>
+        <v>6739052</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,30 +1190,39 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linn Grejs, Cecilia Rastad, Lars-Erik Nilsson</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121643705</v>
+        <v>121635412</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1351,40 +1351,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ol-Larsbo, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530609</v>
+        <v>530656</v>
       </c>
       <c r="R8" t="n">
-        <v>6739158</v>
+        <v>6739100</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1411,40 +1416,49 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linn Grejs, Cecilia Rastad, Lars-Erik Nilsson</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121635412</v>
+        <v>121645979</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,45 +1471,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>10, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530656</v>
+        <v>530657</v>
       </c>
       <c r="R9" t="n">
-        <v>6739100</v>
+        <v>6739025</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1522,46 +1531,37 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs, Cecilia Rastad, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121632944</v>
+        <v>121633817</v>
       </c>
       <c r="B10" t="n">
         <v>78616</v>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530510</v>
+        <v>530605</v>
       </c>
       <c r="R10" t="n">
-        <v>6739257</v>
+        <v>6739161</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121656049</v>
+        <v>121541052</v>
       </c>
       <c r="B11" t="n">
-        <v>57373</v>
+        <v>56561</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,16 +1689,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1706,24 +1706,40 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>13, Dlr</t>
+          <t>9, Fjällgrycken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530570</v>
+        <v>530653</v>
       </c>
       <c r="R11" t="n">
-        <v>6739299</v>
+        <v>6739025</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1747,12 +1763,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1779,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121632076</v>
+        <v>121632944</v>
       </c>
       <c r="B12" t="n">
-        <v>8436</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1791,25 +1807,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1819,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>530487</v>
+        <v>530510</v>
       </c>
       <c r="R12" t="n">
-        <v>6739191</v>
+        <v>6739257</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1854,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1864,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1891,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121541052</v>
+        <v>121656060</v>
       </c>
       <c r="B13" t="n">
-        <v>56561</v>
+        <v>57373</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1907,16 +1923,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1924,40 +1940,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>9, Fjällgrycken, Dlr</t>
+          <t>14, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530653</v>
+        <v>530597</v>
       </c>
       <c r="R13" t="n">
-        <v>6739025</v>
+        <v>6739160</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2119,10 +2119,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121540996</v>
+        <v>121632076</v>
       </c>
       <c r="B15" t="n">
-        <v>91168</v>
+        <v>8436</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2131,44 +2131,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>7, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530649</v>
+        <v>530487</v>
       </c>
       <c r="R15" t="n">
-        <v>6739106</v>
+        <v>6739191</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2192,12 +2189,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2206,29 +2213,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121631841</v>
+        <v>121656049</v>
       </c>
       <c r="B16" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2241,37 +2247,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>13, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>530484</v>
+        <v>530570</v>
       </c>
       <c r="R16" t="n">
-        <v>6739192</v>
+        <v>6739299</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2298,19 +2308,9 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:12</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2325,19 +2325,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121647286</v>
+        <v>121633302</v>
       </c>
       <c r="B17" t="n">
         <v>78616</v>
@@ -2371,19 +2371,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fjällgrycksån,, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>530655</v>
+        <v>530588</v>
       </c>
       <c r="R17" t="n">
-        <v>6739083</v>
+        <v>6739210</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2415,7 +2412,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2425,7 +2422,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2434,7 +2431,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2446,17 +2442,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lars-Erik Nilsson, Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121632920</v>
+        <v>121656035</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2469,37 +2465,41 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>12, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>530531</v>
+        <v>530558</v>
       </c>
       <c r="R18" t="n">
-        <v>6739254</v>
+        <v>6739302</v>
       </c>
       <c r="S18" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2526,19 +2526,9 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2553,19 +2543,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121632008</v>
+        <v>121647286</v>
       </c>
       <c r="B19" t="n">
         <v>78616</v>
@@ -2599,16 +2589,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>Fjällgrycksån,, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>530493</v>
+        <v>530655</v>
       </c>
       <c r="R19" t="n">
-        <v>6739190</v>
+        <v>6739083</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2640,7 +2633,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2650,7 +2643,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2659,6 +2652,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2670,7 +2664,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Cecilia Rastad, Lars-Erik Nilsson, Linn Grejs</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2789,10 +2783,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121656060</v>
+        <v>121632008</v>
       </c>
       <c r="B21" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2805,41 +2799,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>14, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530597</v>
+        <v>530493</v>
       </c>
       <c r="R21" t="n">
-        <v>6739160</v>
+        <v>6739190</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2866,9 +2856,19 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2883,19 +2883,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121633817</v>
+        <v>121631841</v>
       </c>
       <c r="B22" t="n">
         <v>78616</v>
@@ -2935,10 +2935,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530605</v>
+        <v>530484</v>
       </c>
       <c r="R22" t="n">
-        <v>6739161</v>
+        <v>6739192</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3007,7 +3007,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121633302</v>
+        <v>121632920</v>
       </c>
       <c r="B23" t="n">
         <v>78616</v>
@@ -3047,13 +3047,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530588</v>
+        <v>530531</v>
       </c>
       <c r="R23" t="n">
-        <v>6739210</v>
+        <v>6739254</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,10 +3119,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121631634</v>
+        <v>121540996</v>
       </c>
       <c r="B24" t="n">
-        <v>8436</v>
+        <v>91168</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3131,41 +3131,44 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>7, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530482</v>
+        <v>530649</v>
       </c>
       <c r="R24" t="n">
-        <v>6739197</v>
+        <v>6739106</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3189,22 +3192,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:02</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:02</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3213,28 +3206,29 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121656035</v>
+        <v>121631634</v>
       </c>
       <c r="B25" t="n">
-        <v>57373</v>
+        <v>8436</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3243,45 +3237,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>12, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>530558</v>
+        <v>530482</v>
       </c>
       <c r="R25" t="n">
-        <v>6739302</v>
+        <v>6739197</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3308,9 +3298,19 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3325,12 +3325,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 64892-2023 artfynd.xlsx
+++ b/artfynd/A 64892-2023 artfynd.xlsx
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121633817</v>
+        <v>121541052</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>56561</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,37 +1577,57 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>9, Fjällgrycken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530605</v>
+        <v>530653</v>
       </c>
       <c r="R10" t="n">
-        <v>6739161</v>
+        <v>6739025</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,22 +1651,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:27</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:27</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1661,22 +1671,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121541052</v>
+        <v>121633817</v>
       </c>
       <c r="B11" t="n">
-        <v>56561</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,57 +1699,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>9, Fjällgrycken, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530653</v>
+        <v>530605</v>
       </c>
       <c r="R11" t="n">
-        <v>6739025</v>
+        <v>6739161</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1763,12 +1753,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,12 +1783,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2119,10 +2119,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121632076</v>
+        <v>121656049</v>
       </c>
       <c r="B15" t="n">
-        <v>8436</v>
+        <v>57373</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2131,41 +2131,45 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>13, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530487</v>
+        <v>530570</v>
       </c>
       <c r="R15" t="n">
-        <v>6739191</v>
+        <v>6739299</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2192,19 +2196,9 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2219,22 +2213,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121656049</v>
+        <v>121632076</v>
       </c>
       <c r="B16" t="n">
-        <v>57373</v>
+        <v>8436</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2243,45 +2237,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>13, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>530570</v>
+        <v>530487</v>
       </c>
       <c r="R16" t="n">
-        <v>6739299</v>
+        <v>6739191</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2308,9 +2298,19 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2325,12 +2325,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 64892-2023 artfynd.xlsx
+++ b/artfynd/A 64892-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121540928</v>
+        <v>121540923</v>
       </c>
       <c r="B2" t="n">
         <v>78616</v>
@@ -714,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>6, Dlr</t>
+          <t>5, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530586</v>
+        <v>530450</v>
       </c>
       <c r="R2" t="n">
-        <v>6739209</v>
+        <v>6739221</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121540923</v>
+        <v>121540928</v>
       </c>
       <c r="B4" t="n">
         <v>78616</v>
@@ -936,14 +936,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>5, Dlr</t>
+          <t>6, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530450</v>
+        <v>530586</v>
       </c>
       <c r="R4" t="n">
-        <v>6739221</v>
+        <v>6739209</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121635669</v>
+        <v>121645979</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,45 +1125,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>10, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530668</v>
+        <v>530657</v>
       </c>
       <c r="R6" t="n">
-        <v>6739052</v>
+        <v>6739025</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,39 +1185,30 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs, Cecilia Rastad, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1335,7 +1321,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121635412</v>
+        <v>121635669</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1373,7 +1359,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1383,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530656</v>
+        <v>530668</v>
       </c>
       <c r="R8" t="n">
-        <v>6739100</v>
+        <v>6739052</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1418,7 +1404,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1414,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,10 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121645979</v>
+        <v>121635412</v>
       </c>
       <c r="B9" t="n">
-        <v>90728</v>
+        <v>57357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,40 +1457,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>10, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530657</v>
+        <v>530656</v>
       </c>
       <c r="R9" t="n">
-        <v>6739025</v>
+        <v>6739100</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1531,40 +1522,49 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linn Grejs, Cecilia Rastad, Lars-Erik Nilsson</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121541052</v>
+        <v>121632076</v>
       </c>
       <c r="B10" t="n">
-        <v>56561</v>
+        <v>8436</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,61 +1573,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>9, Fjällgrycken, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530653</v>
+        <v>530487</v>
       </c>
       <c r="R10" t="n">
-        <v>6739025</v>
+        <v>6739191</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1651,12 +1631,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,22 +1661,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121633817</v>
+        <v>121541039</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,37 +1689,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>8, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530605</v>
+        <v>530628</v>
       </c>
       <c r="R11" t="n">
-        <v>6739161</v>
+        <v>6739034</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1753,22 +1746,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:27</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:27</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1777,25 +1760,26 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121632944</v>
+        <v>121647286</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1829,16 +1813,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>Fjällgrycksån,, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>530510</v>
+        <v>530655</v>
       </c>
       <c r="R12" t="n">
-        <v>6739257</v>
+        <v>6739083</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1857,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1867,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1889,6 +1876,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1900,14 +1888,14 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Cecilia Rastad, Lars-Erik Nilsson, Linn Grejs</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121656060</v>
+        <v>121656049</v>
       </c>
       <c r="B13" t="n">
         <v>57373</v>
@@ -1947,14 +1935,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>14, Dlr</t>
+          <t>13, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530597</v>
+        <v>530570</v>
       </c>
       <c r="R13" t="n">
-        <v>6739160</v>
+        <v>6739299</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2013,10 +2001,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121541039</v>
+        <v>121632008</v>
       </c>
       <c r="B14" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2029,40 +2017,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>8, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530628</v>
+        <v>530493</v>
       </c>
       <c r="R14" t="n">
-        <v>6739034</v>
+        <v>6739190</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2086,12 +2071,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2100,29 +2095,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121656049</v>
+        <v>121631713</v>
       </c>
       <c r="B15" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2135,41 +2129,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>13, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530570</v>
+        <v>530489</v>
       </c>
       <c r="R15" t="n">
-        <v>6739299</v>
+        <v>6739205</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2196,9 +2186,19 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2213,22 +2213,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121632076</v>
+        <v>121631841</v>
       </c>
       <c r="B16" t="n">
-        <v>8436</v>
+        <v>78616</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2237,25 +2237,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>530487</v>
+        <v>530484</v>
       </c>
       <c r="R16" t="n">
-        <v>6739191</v>
+        <v>6739192</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2337,7 +2337,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121633302</v>
+        <v>121633817</v>
       </c>
       <c r="B17" t="n">
         <v>78616</v>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>530588</v>
+        <v>530605</v>
       </c>
       <c r="R17" t="n">
-        <v>6739210</v>
+        <v>6739161</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2449,10 +2449,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121656035</v>
+        <v>121632920</v>
       </c>
       <c r="B18" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2465,41 +2465,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>12, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>530558</v>
+        <v>530531</v>
       </c>
       <c r="R18" t="n">
-        <v>6739302</v>
+        <v>6739254</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2526,9 +2522,19 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2543,22 +2549,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121647286</v>
+        <v>121656060</v>
       </c>
       <c r="B19" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2571,40 +2577,41 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fjällgrycksån,, Dlr</t>
+          <t>14, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>530655</v>
+        <v>530597</v>
       </c>
       <c r="R19" t="n">
-        <v>6739083</v>
+        <v>6739160</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2631,50 +2638,39 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lars-Erik Nilsson, Linn Grejs</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121631713</v>
+        <v>121631634</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>8436</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2683,25 +2679,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2711,10 +2707,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530489</v>
+        <v>530482</v>
       </c>
       <c r="R20" t="n">
-        <v>6739205</v>
+        <v>6739197</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2746,7 +2742,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2756,7 +2752,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,7 +2779,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121632008</v>
+        <v>121632944</v>
       </c>
       <c r="B21" t="n">
         <v>78616</v>
@@ -2823,10 +2819,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530493</v>
+        <v>530510</v>
       </c>
       <c r="R21" t="n">
-        <v>6739190</v>
+        <v>6739257</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2858,7 +2854,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2868,7 +2864,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2895,10 +2891,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121631841</v>
+        <v>121540996</v>
       </c>
       <c r="B22" t="n">
-        <v>78616</v>
+        <v>91168</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2907,41 +2903,44 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>7, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530484</v>
+        <v>530649</v>
       </c>
       <c r="R22" t="n">
-        <v>6739192</v>
+        <v>6739106</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2965,22 +2964,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:12</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:12</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,25 +2978,26 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121632920</v>
+        <v>121633302</v>
       </c>
       <c r="B23" t="n">
         <v>78616</v>
@@ -3047,13 +3037,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530531</v>
+        <v>530588</v>
       </c>
       <c r="R23" t="n">
-        <v>6739254</v>
+        <v>6739210</v>
       </c>
       <c r="S23" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3082,7 +3072,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3092,7 +3082,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,10 +3109,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121540996</v>
+        <v>121656035</v>
       </c>
       <c r="B24" t="n">
-        <v>91168</v>
+        <v>57373</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3131,44 +3121,45 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>7, Dlr</t>
+          <t>12, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530649</v>
+        <v>530558</v>
       </c>
       <c r="R24" t="n">
-        <v>6739106</v>
+        <v>6739302</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3192,12 +3183,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3206,7 +3197,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3225,10 +3215,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121631634</v>
+        <v>121541052</v>
       </c>
       <c r="B25" t="n">
-        <v>8436</v>
+        <v>56561</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3237,41 +3227,61 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>9, Fjällgrycken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>530482</v>
+        <v>530653</v>
       </c>
       <c r="R25" t="n">
-        <v>6739197</v>
+        <v>6739025</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3295,22 +3305,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:02</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:02</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3325,12 +3325,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 64892-2023 artfynd.xlsx
+++ b/artfynd/A 64892-2023 artfynd.xlsx
@@ -1673,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121541039</v>
+        <v>121647286</v>
       </c>
       <c r="B11" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,21 +1689,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1712,17 +1712,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>8, Dlr</t>
+          <t>Fjällgrycksån,, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530628</v>
+        <v>530655</v>
       </c>
       <c r="R11" t="n">
-        <v>6739034</v>
+        <v>6739083</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1746,12 +1746,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,22 +1777,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Lars-Erik Nilsson, Linn Grejs</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121647286</v>
+        <v>121541039</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1795,21 +1805,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1818,17 +1828,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fjällgrycksån,, Dlr</t>
+          <t>8, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>530655</v>
+        <v>530628</v>
       </c>
       <c r="R12" t="n">
-        <v>6739083</v>
+        <v>6739034</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1852,22 +1862,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1883,12 +1883,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lars-Erik Nilsson, Linn Grejs</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 64892-2023 artfynd.xlsx
+++ b/artfynd/A 64892-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121540923</v>
+        <v>121540928</v>
       </c>
       <c r="B2" t="n">
         <v>78616</v>
@@ -714,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>5, Dlr</t>
+          <t>6, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530450</v>
+        <v>530586</v>
       </c>
       <c r="R2" t="n">
-        <v>6739221</v>
+        <v>6739209</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121540928</v>
+        <v>121540923</v>
       </c>
       <c r="B4" t="n">
         <v>78616</v>
@@ -936,14 +936,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>6, Dlr</t>
+          <t>5, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530586</v>
+        <v>530450</v>
       </c>
       <c r="R4" t="n">
-        <v>6739209</v>
+        <v>6739221</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121643705</v>
+        <v>121635412</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,40 +1019,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ol-Larsbo, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530609</v>
+        <v>530656</v>
       </c>
       <c r="R5" t="n">
-        <v>6739158</v>
+        <v>6739100</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,40 +1084,49 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Cecilia Rastad, Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121645979</v>
+        <v>121643705</v>
       </c>
       <c r="B6" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,14 +1162,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>10, Dlr</t>
+          <t>Ol-Larsbo, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530657</v>
+        <v>530609</v>
       </c>
       <c r="R6" t="n">
-        <v>6739025</v>
+        <v>6739158</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1203,12 +1217,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linn Grejs, Cecilia Rastad, Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Cecilia Rastad, Linn Grejs</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1441,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121635412</v>
+        <v>121645979</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,45 +1471,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>10, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530656</v>
+        <v>530657</v>
       </c>
       <c r="R9" t="n">
-        <v>6739100</v>
+        <v>6739025</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1522,49 +1531,40 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs, Cecilia Rastad, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121632076</v>
+        <v>121540996</v>
       </c>
       <c r="B10" t="n">
-        <v>8436</v>
+        <v>91168</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,41 +1573,44 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>7, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530487</v>
+        <v>530649</v>
       </c>
       <c r="R10" t="n">
-        <v>6739191</v>
+        <v>6739106</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,22 +1634,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,25 +1648,26 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121647286</v>
+        <v>121631713</v>
       </c>
       <c r="B11" t="n">
         <v>78616</v>
@@ -1707,19 +1701,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fjällgrycksån,, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530655</v>
+        <v>530489</v>
       </c>
       <c r="R11" t="n">
-        <v>6739083</v>
+        <v>6739205</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1751,7 +1742,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1761,7 +1752,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,7 +1761,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1782,17 +1772,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lars-Erik Nilsson, Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121541039</v>
+        <v>121656049</v>
       </c>
       <c r="B12" t="n">
-        <v>90728</v>
+        <v>57373</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1805,40 +1795,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>8, Dlr</t>
+          <t>13, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>530628</v>
+        <v>530570</v>
       </c>
       <c r="R12" t="n">
-        <v>6739034</v>
+        <v>6739299</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1862,12 +1853,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,7 +1867,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1895,10 +1885,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121656049</v>
+        <v>121631634</v>
       </c>
       <c r="B13" t="n">
-        <v>57373</v>
+        <v>8436</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1907,45 +1897,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>13, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530570</v>
+        <v>530482</v>
       </c>
       <c r="R13" t="n">
-        <v>6739299</v>
+        <v>6739197</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,9 +1958,19 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,22 +1985,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121632008</v>
+        <v>121541052</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
+        <v>56561</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2017,37 +2013,57 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>9, Fjällgrycken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530493</v>
+        <v>530653</v>
       </c>
       <c r="R14" t="n">
-        <v>6739190</v>
+        <v>6739025</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2071,22 +2087,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2101,19 +2107,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121631713</v>
+        <v>121633302</v>
       </c>
       <c r="B15" t="n">
         <v>78616</v>
@@ -2153,10 +2159,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530489</v>
+        <v>530588</v>
       </c>
       <c r="R15" t="n">
-        <v>6739205</v>
+        <v>6739210</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2188,7 +2194,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2198,7 +2204,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2225,7 +2231,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121631841</v>
+        <v>121632944</v>
       </c>
       <c r="B16" t="n">
         <v>78616</v>
@@ -2265,10 +2271,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>530484</v>
+        <v>530510</v>
       </c>
       <c r="R16" t="n">
-        <v>6739192</v>
+        <v>6739257</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2300,7 +2306,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2310,7 +2316,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2337,7 +2343,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121633817</v>
+        <v>121632008</v>
       </c>
       <c r="B17" t="n">
         <v>78616</v>
@@ -2377,10 +2383,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>530605</v>
+        <v>530493</v>
       </c>
       <c r="R17" t="n">
-        <v>6739161</v>
+        <v>6739190</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2412,7 +2418,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2422,7 +2428,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2449,7 +2455,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121632920</v>
+        <v>121631841</v>
       </c>
       <c r="B18" t="n">
         <v>78616</v>
@@ -2489,13 +2495,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>530531</v>
+        <v>530484</v>
       </c>
       <c r="R18" t="n">
-        <v>6739254</v>
+        <v>6739192</v>
       </c>
       <c r="S18" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2524,7 +2530,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2534,7 +2540,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2561,10 +2567,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121656060</v>
+        <v>121632076</v>
       </c>
       <c r="B19" t="n">
-        <v>57373</v>
+        <v>8436</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2573,45 +2579,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>14, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>530597</v>
+        <v>530487</v>
       </c>
       <c r="R19" t="n">
-        <v>6739160</v>
+        <v>6739191</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2638,9 +2640,19 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2655,22 +2667,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121631634</v>
+        <v>121647286</v>
       </c>
       <c r="B20" t="n">
-        <v>8436</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2679,38 +2691,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>Fjällgrycksån,, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530482</v>
+        <v>530655</v>
       </c>
       <c r="R20" t="n">
-        <v>6739197</v>
+        <v>6739083</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2742,7 +2757,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2752,7 +2767,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2761,6 +2776,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2772,17 +2788,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Cecilia Rastad, Lars-Erik Nilsson, Linn Grejs</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121632944</v>
+        <v>121656060</v>
       </c>
       <c r="B21" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2795,37 +2811,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>14, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530510</v>
+        <v>530597</v>
       </c>
       <c r="R21" t="n">
-        <v>6739257</v>
+        <v>6739160</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2852,19 +2872,9 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2879,22 +2889,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121540996</v>
+        <v>121656035</v>
       </c>
       <c r="B22" t="n">
-        <v>91168</v>
+        <v>57373</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2903,44 +2913,45 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>7, Dlr</t>
+          <t>12, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530649</v>
+        <v>530558</v>
       </c>
       <c r="R22" t="n">
-        <v>6739106</v>
+        <v>6739302</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2964,12 +2975,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2978,7 +2989,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2997,7 +3007,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121633302</v>
+        <v>121633817</v>
       </c>
       <c r="B23" t="n">
         <v>78616</v>
@@ -3037,10 +3047,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530588</v>
+        <v>530605</v>
       </c>
       <c r="R23" t="n">
-        <v>6739210</v>
+        <v>6739161</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3072,7 +3082,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3082,7 +3092,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3109,10 +3119,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121656035</v>
+        <v>121632920</v>
       </c>
       <c r="B24" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3125,41 +3135,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>12, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530558</v>
+        <v>530531</v>
       </c>
       <c r="R24" t="n">
-        <v>6739302</v>
+        <v>6739254</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3186,9 +3192,19 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3203,22 +3219,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121541052</v>
+        <v>121541039</v>
       </c>
       <c r="B25" t="n">
-        <v>56561</v>
+        <v>90728</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3231,54 +3247,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>9, Fjällgrycken, Dlr</t>
+          <t>8, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>530653</v>
+        <v>530628</v>
       </c>
       <c r="R25" t="n">
-        <v>6739025</v>
+        <v>6739034</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3319,6 +3318,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64892-2023 artfynd.xlsx
+++ b/artfynd/A 64892-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121540928</v>
+        <v>121540816</v>
       </c>
       <c r="B2" t="n">
         <v>78616</v>
@@ -714,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>6, Dlr</t>
+          <t>2, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530586</v>
+        <v>530491</v>
       </c>
       <c r="R2" t="n">
-        <v>6739209</v>
+        <v>6739260</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,9 +751,19 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121540816</v>
+        <v>121540923</v>
       </c>
       <c r="B3" t="n">
         <v>78616</v>
@@ -820,14 +830,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2, Dlr</t>
+          <t>5, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530491</v>
+        <v>530450</v>
       </c>
       <c r="R3" t="n">
-        <v>6739260</v>
+        <v>6739221</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,19 +867,9 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121540923</v>
+        <v>121540928</v>
       </c>
       <c r="B4" t="n">
         <v>78616</v>
@@ -936,14 +936,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>5, Dlr</t>
+          <t>6, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530450</v>
+        <v>530586</v>
       </c>
       <c r="R4" t="n">
-        <v>6739221</v>
+        <v>6739209</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,7 +1003,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121635412</v>
+        <v>121635669</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1041,7 +1041,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530656</v>
+        <v>530668</v>
       </c>
       <c r="R5" t="n">
-        <v>6739100</v>
+        <v>6739052</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1229,7 +1229,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121645997</v>
+        <v>121645979</v>
       </c>
       <c r="B7" t="n">
         <v>90728</v>
@@ -1268,14 +1268,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>11, Dlr</t>
+          <t>10, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530662</v>
+        <v>530657</v>
       </c>
       <c r="R7" t="n">
-        <v>6739074</v>
+        <v>6739025</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1335,7 +1335,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121635669</v>
+        <v>121635412</v>
       </c>
       <c r="B8" t="n">
         <v>57357</v>
@@ -1373,7 +1373,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530668</v>
+        <v>530656</v>
       </c>
       <c r="R8" t="n">
-        <v>6739052</v>
+        <v>6739100</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,7 +1455,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121645979</v>
+        <v>121645997</v>
       </c>
       <c r="B9" t="n">
         <v>90728</v>
@@ -1494,14 +1494,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>10, Dlr</t>
+          <t>11, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530657</v>
+        <v>530662</v>
       </c>
       <c r="R9" t="n">
-        <v>6739025</v>
+        <v>6739074</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121540996</v>
+        <v>121631841</v>
       </c>
       <c r="B10" t="n">
-        <v>91168</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,44 +1573,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>7, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530649</v>
+        <v>530484</v>
       </c>
       <c r="R10" t="n">
-        <v>6739106</v>
+        <v>6739192</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1634,12 +1631,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,26 +1655,25 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121631713</v>
+        <v>121632008</v>
       </c>
       <c r="B11" t="n">
         <v>78616</v>
@@ -1707,10 +1713,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530489</v>
+        <v>530493</v>
       </c>
       <c r="R11" t="n">
-        <v>6739205</v>
+        <v>6739190</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1742,7 +1748,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1752,7 +1758,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1779,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121656049</v>
+        <v>121541052</v>
       </c>
       <c r="B12" t="n">
-        <v>57373</v>
+        <v>56561</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1795,16 +1801,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1812,24 +1818,40 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>13, Dlr</t>
+          <t>9, Fjällgrycken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>530570</v>
+        <v>530653</v>
       </c>
       <c r="R12" t="n">
-        <v>6739299</v>
+        <v>6739025</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1853,12 +1875,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1885,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121631634</v>
+        <v>121540996</v>
       </c>
       <c r="B13" t="n">
-        <v>8436</v>
+        <v>91168</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1897,41 +1919,44 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>7, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530482</v>
+        <v>530649</v>
       </c>
       <c r="R13" t="n">
-        <v>6739197</v>
+        <v>6739106</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1955,22 +1980,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:02</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:02</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,28 +1994,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121541052</v>
+        <v>121632076</v>
       </c>
       <c r="B14" t="n">
-        <v>56561</v>
+        <v>8436</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2009,61 +2025,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>9, Fjällgrycken, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530653</v>
+        <v>530487</v>
       </c>
       <c r="R14" t="n">
-        <v>6739025</v>
+        <v>6739191</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2087,12 +2083,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2107,12 +2113,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2231,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121632944</v>
+        <v>121656035</v>
       </c>
       <c r="B16" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2247,37 +2253,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>12, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>530510</v>
+        <v>530558</v>
       </c>
       <c r="R16" t="n">
-        <v>6739257</v>
+        <v>6739302</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2304,19 +2314,9 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2331,22 +2331,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121632008</v>
+        <v>121656049</v>
       </c>
       <c r="B17" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2359,37 +2359,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>13, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>530493</v>
+        <v>530570</v>
       </c>
       <c r="R17" t="n">
-        <v>6739190</v>
+        <v>6739299</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2416,19 +2420,9 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2443,19 +2437,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121631841</v>
+        <v>121632944</v>
       </c>
       <c r="B18" t="n">
         <v>78616</v>
@@ -2495,10 +2489,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>530484</v>
+        <v>530510</v>
       </c>
       <c r="R18" t="n">
-        <v>6739192</v>
+        <v>6739257</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2530,7 +2524,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2540,7 +2534,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2567,10 +2561,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121632076</v>
+        <v>121647286</v>
       </c>
       <c r="B19" t="n">
-        <v>8436</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2579,38 +2573,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>Fjällgrycksån,, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>530487</v>
+        <v>530655</v>
       </c>
       <c r="R19" t="n">
-        <v>6739191</v>
+        <v>6739083</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2642,7 +2639,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2652,7 +2649,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2661,6 +2658,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2672,17 +2670,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Cecilia Rastad, Lars-Erik Nilsson, Linn Grejs</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121647286</v>
+        <v>121631634</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>8436</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2691,41 +2689,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fjällgrycksån,, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530655</v>
+        <v>530482</v>
       </c>
       <c r="R20" t="n">
-        <v>6739083</v>
+        <v>6739197</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2757,7 +2752,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2767,7 +2762,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2776,7 +2771,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2788,17 +2782,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lars-Erik Nilsson, Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121656060</v>
+        <v>121632920</v>
       </c>
       <c r="B21" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2811,41 +2805,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>14, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530597</v>
+        <v>530531</v>
       </c>
       <c r="R21" t="n">
-        <v>6739160</v>
+        <v>6739254</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2872,9 +2862,19 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2889,22 +2889,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121656035</v>
+        <v>121633817</v>
       </c>
       <c r="B22" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2917,41 +2917,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>12, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530558</v>
+        <v>530605</v>
       </c>
       <c r="R22" t="n">
-        <v>6739302</v>
+        <v>6739161</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2978,9 +2974,19 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2995,19 +3001,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121633817</v>
+        <v>121631713</v>
       </c>
       <c r="B23" t="n">
         <v>78616</v>
@@ -3047,10 +3053,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530605</v>
+        <v>530489</v>
       </c>
       <c r="R23" t="n">
-        <v>6739161</v>
+        <v>6739205</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3082,7 +3088,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3092,7 +3098,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,10 +3125,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121632920</v>
+        <v>121656060</v>
       </c>
       <c r="B24" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3135,37 +3141,41 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>14, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530531</v>
+        <v>530597</v>
       </c>
       <c r="R24" t="n">
-        <v>6739254</v>
+        <v>6739160</v>
       </c>
       <c r="S24" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3192,19 +3202,9 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3219,12 +3219,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 64892-2023 artfynd.xlsx
+++ b/artfynd/A 64892-2023 artfynd.xlsx
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121540923</v>
+        <v>121540928</v>
       </c>
       <c r="B3" t="n">
         <v>78616</v>
@@ -830,14 +830,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>5, Dlr</t>
+          <t>6, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530450</v>
+        <v>530586</v>
       </c>
       <c r="R3" t="n">
-        <v>6739221</v>
+        <v>6739209</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121540928</v>
+        <v>121540923</v>
       </c>
       <c r="B4" t="n">
         <v>78616</v>
@@ -936,14 +936,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>6, Dlr</t>
+          <t>5, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530586</v>
+        <v>530450</v>
       </c>
       <c r="R4" t="n">
-        <v>6739209</v>
+        <v>6739221</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121635669</v>
+        <v>121645979</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,45 +1019,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>10, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530668</v>
+        <v>530657</v>
       </c>
       <c r="R5" t="n">
-        <v>6739052</v>
+        <v>6739025</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,49 +1079,40 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs, Cecilia Rastad, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121643705</v>
+        <v>121635412</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,40 +1125,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ol-Larsbo, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530609</v>
+        <v>530656</v>
       </c>
       <c r="R6" t="n">
-        <v>6739158</v>
+        <v>6739100</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,40 +1190,49 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Cecilia Rastad, Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121645979</v>
+        <v>121635669</v>
       </c>
       <c r="B7" t="n">
-        <v>90728</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,40 +1245,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>10, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530657</v>
+        <v>530668</v>
       </c>
       <c r="R7" t="n">
-        <v>6739025</v>
+        <v>6739052</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,40 +1310,49 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linn Grejs, Cecilia Rastad, Lars-Erik Nilsson</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121635412</v>
+        <v>121645997</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1351,45 +1365,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>11, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530656</v>
+        <v>530662</v>
       </c>
       <c r="R8" t="n">
-        <v>6739100</v>
+        <v>6739074</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1416,49 +1425,40 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs, Cecilia Rastad, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121645997</v>
+        <v>121643705</v>
       </c>
       <c r="B9" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,14 +1494,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>11, Dlr</t>
+          <t>Ol-Larsbo, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530662</v>
+        <v>530609</v>
       </c>
       <c r="R9" t="n">
-        <v>6739074</v>
+        <v>6739158</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1549,22 +1549,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linn Grejs, Cecilia Rastad, Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Cecilia Rastad, Linn Grejs</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121631841</v>
+        <v>121631634</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>8436</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,25 +1573,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530484</v>
+        <v>530482</v>
       </c>
       <c r="R10" t="n">
-        <v>6739192</v>
+        <v>6739197</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121632008</v>
+        <v>121656060</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,37 +1689,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>14, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530493</v>
+        <v>530597</v>
       </c>
       <c r="R11" t="n">
-        <v>6739190</v>
+        <v>6739160</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1746,19 +1750,9 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1773,22 +1767,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121541052</v>
+        <v>121631841</v>
       </c>
       <c r="B12" t="n">
-        <v>56561</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,57 +1795,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>9, Fjällgrycken, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>530653</v>
+        <v>530484</v>
       </c>
       <c r="R12" t="n">
-        <v>6739025</v>
+        <v>6739192</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1875,12 +1849,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,22 +1879,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121540996</v>
+        <v>121633302</v>
       </c>
       <c r="B13" t="n">
-        <v>91168</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,44 +1903,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>7, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530649</v>
+        <v>530588</v>
       </c>
       <c r="R13" t="n">
-        <v>6739106</v>
+        <v>6739210</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1980,12 +1961,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1994,29 +1985,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121632076</v>
+        <v>121633817</v>
       </c>
       <c r="B14" t="n">
-        <v>8436</v>
+        <v>78616</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2025,25 +2015,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2053,10 +2043,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530487</v>
+        <v>530605</v>
       </c>
       <c r="R14" t="n">
-        <v>6739191</v>
+        <v>6739161</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2088,7 +2078,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2098,7 +2088,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2125,7 +2115,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121633302</v>
+        <v>121632008</v>
       </c>
       <c r="B15" t="n">
         <v>78616</v>
@@ -2165,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530588</v>
+        <v>530493</v>
       </c>
       <c r="R15" t="n">
-        <v>6739210</v>
+        <v>6739190</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2200,7 +2190,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2200,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,10 +2227,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121656035</v>
+        <v>121540996</v>
       </c>
       <c r="B16" t="n">
-        <v>57373</v>
+        <v>91168</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2249,45 +2239,44 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>12, Dlr</t>
+          <t>7, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>530558</v>
+        <v>530649</v>
       </c>
       <c r="R16" t="n">
-        <v>6739302</v>
+        <v>6739106</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2311,12 +2300,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2325,6 +2314,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2343,10 +2333,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121656049</v>
+        <v>121647286</v>
       </c>
       <c r="B17" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2359,41 +2349,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>13, Dlr</t>
+          <t>Fjällgrycksån,, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>530570</v>
+        <v>530655</v>
       </c>
       <c r="R17" t="n">
-        <v>6739299</v>
+        <v>6739083</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2420,39 +2409,50 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Lars-Erik Nilsson, Linn Grejs</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121632944</v>
+        <v>121656035</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2465,37 +2465,41 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>12, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>530510</v>
+        <v>530558</v>
       </c>
       <c r="R18" t="n">
-        <v>6739257</v>
+        <v>6739302</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2522,19 +2526,9 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2549,22 +2543,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121647286</v>
+        <v>121656049</v>
       </c>
       <c r="B19" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2577,40 +2571,41 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fjällgrycksån,, Dlr</t>
+          <t>13, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>530655</v>
+        <v>530570</v>
       </c>
       <c r="R19" t="n">
-        <v>6739083</v>
+        <v>6739299</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2637,50 +2632,39 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lars-Erik Nilsson, Linn Grejs</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121631634</v>
+        <v>121632920</v>
       </c>
       <c r="B20" t="n">
-        <v>8436</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2689,25 +2673,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2717,13 +2701,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530482</v>
+        <v>530531</v>
       </c>
       <c r="R20" t="n">
-        <v>6739197</v>
+        <v>6739254</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2752,7 +2736,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2762,7 +2746,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2789,7 +2773,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121632920</v>
+        <v>121631713</v>
       </c>
       <c r="B21" t="n">
         <v>78616</v>
@@ -2829,13 +2813,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530531</v>
+        <v>530489</v>
       </c>
       <c r="R21" t="n">
-        <v>6739254</v>
+        <v>6739205</v>
       </c>
       <c r="S21" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2864,7 +2848,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2874,7 +2858,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2901,7 +2885,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121633817</v>
+        <v>121632944</v>
       </c>
       <c r="B22" t="n">
         <v>78616</v>
@@ -2941,10 +2925,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530605</v>
+        <v>530510</v>
       </c>
       <c r="R22" t="n">
-        <v>6739161</v>
+        <v>6739257</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2976,7 +2960,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2986,7 +2970,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3013,10 +2997,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121631713</v>
+        <v>121541039</v>
       </c>
       <c r="B23" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3029,37 +3013,40 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>8, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530489</v>
+        <v>530628</v>
       </c>
       <c r="R23" t="n">
-        <v>6739205</v>
+        <v>6739034</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3083,22 +3070,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:08</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:08</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3107,28 +3084,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121656060</v>
+        <v>121632076</v>
       </c>
       <c r="B24" t="n">
-        <v>57373</v>
+        <v>8436</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3137,45 +3115,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>14, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530597</v>
+        <v>530487</v>
       </c>
       <c r="R24" t="n">
-        <v>6739160</v>
+        <v>6739191</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3202,9 +3176,19 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3219,22 +3203,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121541039</v>
+        <v>121541052</v>
       </c>
       <c r="B25" t="n">
-        <v>90728</v>
+        <v>56561</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3247,37 +3231,54 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>8, Dlr</t>
+          <t>9, Fjällgrycken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>530628</v>
+        <v>530653</v>
       </c>
       <c r="R25" t="n">
-        <v>6739034</v>
+        <v>6739025</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3318,7 +3319,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64892-2023 artfynd.xlsx
+++ b/artfynd/A 64892-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121540816</v>
+        <v>121540928</v>
       </c>
       <c r="B2" t="n">
         <v>78616</v>
@@ -714,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2, Dlr</t>
+          <t>6, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530491</v>
+        <v>530586</v>
       </c>
       <c r="R2" t="n">
-        <v>6739260</v>
+        <v>6739209</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +751,9 @@
           <t>2024-12-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121540928</v>
+        <v>121540816</v>
       </c>
       <c r="B3" t="n">
         <v>78616</v>
@@ -830,14 +820,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>6, Dlr</t>
+          <t>2, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530586</v>
+        <v>530491</v>
       </c>
       <c r="R3" t="n">
-        <v>6739209</v>
+        <v>6739260</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,9 +857,19 @@
           <t>2024-12-09</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121645979</v>
+        <v>121635412</v>
       </c>
       <c r="B5" t="n">
-        <v>90728</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,40 +1019,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>10, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530657</v>
+        <v>530656</v>
       </c>
       <c r="R5" t="n">
-        <v>6739025</v>
+        <v>6739100</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,37 +1084,46 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linn Grejs, Cecilia Rastad, Lars-Erik Nilsson</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121635412</v>
+        <v>121635669</v>
       </c>
       <c r="B6" t="n">
         <v>57357</v>
@@ -1147,7 +1161,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1157,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530656</v>
+        <v>530668</v>
       </c>
       <c r="R6" t="n">
-        <v>6739100</v>
+        <v>6739052</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1192,7 +1206,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1216,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121635669</v>
+        <v>121645997</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,45 +1259,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>11, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530668</v>
+        <v>530662</v>
       </c>
       <c r="R7" t="n">
-        <v>6739052</v>
+        <v>6739074</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,46 +1319,37 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Cecilia Rastad, Linn Grejs</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121645997</v>
+        <v>121645979</v>
       </c>
       <c r="B8" t="n">
         <v>90728</v>
@@ -1388,14 +1388,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>11, Dlr</t>
+          <t>10, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530662</v>
+        <v>530657</v>
       </c>
       <c r="R8" t="n">
-        <v>6739074</v>
+        <v>6739025</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121631634</v>
+        <v>121633302</v>
       </c>
       <c r="B10" t="n">
-        <v>8436</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,25 +1573,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530482</v>
+        <v>530588</v>
       </c>
       <c r="R10" t="n">
-        <v>6739197</v>
+        <v>6739210</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121656060</v>
+        <v>121647286</v>
       </c>
       <c r="B11" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,41 +1689,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>14, Dlr</t>
+          <t>Fjällgrycksån,, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530597</v>
+        <v>530655</v>
       </c>
       <c r="R11" t="n">
-        <v>6739160</v>
+        <v>6739083</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1750,36 +1749,47 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Lars-Erik Nilsson, Linn Grejs</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121631841</v>
+        <v>121631713</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1819,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>530484</v>
+        <v>530489</v>
       </c>
       <c r="R12" t="n">
-        <v>6739192</v>
+        <v>6739205</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1854,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1864,7 +1874,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1891,7 +1901,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121633302</v>
+        <v>121632920</v>
       </c>
       <c r="B13" t="n">
         <v>78616</v>
@@ -1931,13 +1941,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530588</v>
+        <v>530531</v>
       </c>
       <c r="R13" t="n">
-        <v>6739210</v>
+        <v>6739254</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,7 +1976,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1986,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,7 +2013,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121633817</v>
+        <v>121632944</v>
       </c>
       <c r="B14" t="n">
         <v>78616</v>
@@ -2043,10 +2053,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530605</v>
+        <v>530510</v>
       </c>
       <c r="R14" t="n">
-        <v>6739161</v>
+        <v>6739257</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2078,7 +2088,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2088,7 +2098,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2115,10 +2125,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121632008</v>
+        <v>121631634</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>8436</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2127,25 +2137,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2155,10 +2165,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530493</v>
+        <v>530482</v>
       </c>
       <c r="R15" t="n">
-        <v>6739190</v>
+        <v>6739197</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2190,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2200,7 +2210,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2227,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121540996</v>
+        <v>121633817</v>
       </c>
       <c r="B16" t="n">
-        <v>91168</v>
+        <v>78616</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2239,44 +2249,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>7, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>530649</v>
+        <v>530605</v>
       </c>
       <c r="R16" t="n">
-        <v>6739106</v>
+        <v>6739161</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2300,12 +2307,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2314,29 +2331,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121647286</v>
+        <v>121656060</v>
       </c>
       <c r="B17" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2349,40 +2365,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fjällgrycksån,, Dlr</t>
+          <t>14, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>530655</v>
+        <v>530597</v>
       </c>
       <c r="R17" t="n">
-        <v>6739083</v>
+        <v>6739160</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2409,50 +2426,39 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lars-Erik Nilsson, Linn Grejs</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121656035</v>
+        <v>121632008</v>
       </c>
       <c r="B18" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2465,41 +2471,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>12, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>530558</v>
+        <v>530493</v>
       </c>
       <c r="R18" t="n">
-        <v>6739302</v>
+        <v>6739190</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2526,9 +2528,19 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2543,12 +2555,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2661,10 +2673,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121632920</v>
+        <v>121656035</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2677,37 +2689,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>12, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530531</v>
+        <v>530558</v>
       </c>
       <c r="R20" t="n">
-        <v>6739254</v>
+        <v>6739302</v>
       </c>
       <c r="S20" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2734,19 +2750,9 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>10:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2761,22 +2767,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121631713</v>
+        <v>121632076</v>
       </c>
       <c r="B21" t="n">
-        <v>78616</v>
+        <v>8436</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2785,25 +2791,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2813,10 +2819,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530489</v>
+        <v>530487</v>
       </c>
       <c r="R21" t="n">
-        <v>6739205</v>
+        <v>6739191</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2848,7 +2854,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2858,7 +2864,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2885,7 +2891,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121632944</v>
+        <v>121631841</v>
       </c>
       <c r="B22" t="n">
         <v>78616</v>
@@ -2925,10 +2931,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530510</v>
+        <v>530484</v>
       </c>
       <c r="R22" t="n">
-        <v>6739257</v>
+        <v>6739192</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2960,7 +2966,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2970,7 +2976,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3103,10 +3109,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121632076</v>
+        <v>121540996</v>
       </c>
       <c r="B24" t="n">
-        <v>8436</v>
+        <v>91168</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3115,41 +3121,44 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>7, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530487</v>
+        <v>530649</v>
       </c>
       <c r="R24" t="n">
-        <v>6739191</v>
+        <v>6739106</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3173,22 +3182,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3197,18 +3196,19 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 64892-2023 artfynd.xlsx
+++ b/artfynd/A 64892-2023 artfynd.xlsx
@@ -2125,10 +2125,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121631634</v>
+        <v>121633817</v>
       </c>
       <c r="B15" t="n">
-        <v>8436</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2137,25 +2137,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530482</v>
+        <v>530605</v>
       </c>
       <c r="R15" t="n">
-        <v>6739197</v>
+        <v>6739161</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121633817</v>
+        <v>121631634</v>
       </c>
       <c r="B16" t="n">
-        <v>78616</v>
+        <v>8436</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2249,25 +2249,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>530605</v>
+        <v>530482</v>
       </c>
       <c r="R16" t="n">
-        <v>6739161</v>
+        <v>6739197</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 64892-2023 artfynd.xlsx
+++ b/artfynd/A 64892-2023 artfynd.xlsx
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121635412</v>
+        <v>121635669</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530656</v>
+        <v>530668</v>
       </c>
       <c r="R5" t="n">
-        <v>6739100</v>
+        <v>6739052</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121635669</v>
+        <v>121645979</v>
       </c>
       <c r="B6" t="n">
-        <v>57357</v>
+        <v>90742</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,45 +1139,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>10, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530668</v>
+        <v>530657</v>
       </c>
       <c r="R6" t="n">
-        <v>6739052</v>
+        <v>6739025</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1204,49 +1199,40 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs, Cecilia Rastad, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121645997</v>
+        <v>121635412</v>
       </c>
       <c r="B7" t="n">
-        <v>90728</v>
+        <v>57365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,40 +1245,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>11, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530662</v>
+        <v>530656</v>
       </c>
       <c r="R7" t="n">
-        <v>6739074</v>
+        <v>6739100</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,40 +1310,49 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Cecilia Rastad, Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121645979</v>
+        <v>121645997</v>
       </c>
       <c r="B8" t="n">
-        <v>90728</v>
+        <v>90742</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,14 +1388,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>10, Dlr</t>
+          <t>11, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530657</v>
+        <v>530662</v>
       </c>
       <c r="R8" t="n">
-        <v>6739025</v>
+        <v>6739074</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1458,7 +1458,7 @@
         <v>121643705</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121633302</v>
+        <v>121540996</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>91182</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,41 +1573,44 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>7, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530588</v>
+        <v>530649</v>
       </c>
       <c r="R10" t="n">
-        <v>6739210</v>
+        <v>6739106</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,22 +1634,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:12</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:12</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,28 +1648,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121647286</v>
+        <v>121631713</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1707,19 +1701,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fjällgrycksån,, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530655</v>
+        <v>530489</v>
       </c>
       <c r="R11" t="n">
-        <v>6739083</v>
+        <v>6739205</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1751,7 +1742,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1761,7 +1752,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,7 +1761,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1782,17 +1772,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lars-Erik Nilsson, Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121631713</v>
+        <v>121632008</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,10 +1819,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>530489</v>
+        <v>530493</v>
       </c>
       <c r="R12" t="n">
-        <v>6739205</v>
+        <v>6739190</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1864,7 +1854,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,7 +1864,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1901,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121632920</v>
+        <v>121656049</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
+        <v>57381</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1917,37 +1907,41 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>13, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530531</v>
+        <v>530570</v>
       </c>
       <c r="R13" t="n">
-        <v>6739254</v>
+        <v>6739299</v>
       </c>
       <c r="S13" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1974,19 +1968,9 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,22 +1985,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121632944</v>
+        <v>121656035</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
+        <v>57381</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2029,37 +2013,41 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>12, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530510</v>
+        <v>530558</v>
       </c>
       <c r="R14" t="n">
-        <v>6739257</v>
+        <v>6739302</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2086,19 +2074,9 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2113,22 +2091,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121633817</v>
+        <v>121632920</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2165,13 +2143,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530605</v>
+        <v>530531</v>
       </c>
       <c r="R15" t="n">
-        <v>6739161</v>
+        <v>6739254</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2200,7 +2178,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2188,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,7 +2215,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121631634</v>
+        <v>121632076</v>
       </c>
       <c r="B16" t="n">
         <v>8436</v>
@@ -2277,10 +2255,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>530482</v>
+        <v>530487</v>
       </c>
       <c r="R16" t="n">
-        <v>6739197</v>
+        <v>6739191</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2312,7 +2290,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2322,7 +2300,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2349,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121656060</v>
+        <v>121632944</v>
       </c>
       <c r="B17" t="n">
-        <v>57373</v>
+        <v>78629</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2365,41 +2343,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>14, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>530597</v>
+        <v>530510</v>
       </c>
       <c r="R17" t="n">
-        <v>6739160</v>
+        <v>6739257</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2426,9 +2400,19 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2443,22 +2427,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121632008</v>
+        <v>121656060</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
+        <v>57381</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2471,37 +2455,41 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>14, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>530493</v>
+        <v>530597</v>
       </c>
       <c r="R18" t="n">
-        <v>6739190</v>
+        <v>6739160</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2528,19 +2516,9 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2555,22 +2533,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121656049</v>
+        <v>121541039</v>
       </c>
       <c r="B19" t="n">
-        <v>57373</v>
+        <v>90742</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2583,41 +2561,40 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>13, Dlr</t>
+          <t>8, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>530570</v>
+        <v>530628</v>
       </c>
       <c r="R19" t="n">
-        <v>6739299</v>
+        <v>6739034</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2641,12 +2618,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2655,6 +2632,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2673,10 +2651,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121656035</v>
+        <v>121633817</v>
       </c>
       <c r="B20" t="n">
-        <v>57373</v>
+        <v>78629</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2689,41 +2667,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>12, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530558</v>
+        <v>530605</v>
       </c>
       <c r="R20" t="n">
-        <v>6739302</v>
+        <v>6739161</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2750,9 +2724,19 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2767,22 +2751,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121632076</v>
+        <v>121631841</v>
       </c>
       <c r="B21" t="n">
-        <v>8436</v>
+        <v>78629</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2791,25 +2775,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2819,10 +2803,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530487</v>
+        <v>530484</v>
       </c>
       <c r="R21" t="n">
-        <v>6739191</v>
+        <v>6739192</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2854,7 +2838,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2864,7 +2848,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2891,10 +2875,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121631841</v>
+        <v>121633302</v>
       </c>
       <c r="B22" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2931,10 +2915,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530484</v>
+        <v>530588</v>
       </c>
       <c r="R22" t="n">
-        <v>6739192</v>
+        <v>6739210</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2966,7 +2950,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2976,7 +2960,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3003,10 +2987,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121541039</v>
+        <v>121647286</v>
       </c>
       <c r="B23" t="n">
-        <v>90728</v>
+        <v>78629</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3019,21 +3003,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3042,17 +3026,17 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>8, Dlr</t>
+          <t>Fjällgrycksån,, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530628</v>
+        <v>530655</v>
       </c>
       <c r="R23" t="n">
-        <v>6739034</v>
+        <v>6739083</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3076,12 +3060,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3097,22 +3091,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Lars-Erik Nilsson, Linn Grejs</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121540996</v>
+        <v>121631634</v>
       </c>
       <c r="B24" t="n">
-        <v>91168</v>
+        <v>8436</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3121,44 +3115,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>7, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530649</v>
+        <v>530482</v>
       </c>
       <c r="R24" t="n">
-        <v>6739106</v>
+        <v>6739197</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3182,12 +3173,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3196,19 +3197,18 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3218,7 +3218,7 @@
         <v>121541052</v>
       </c>
       <c r="B25" t="n">
-        <v>56561</v>
+        <v>56569</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 64892-2023 artfynd.xlsx
+++ b/artfynd/A 64892-2023 artfynd.xlsx
@@ -1349,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121645997</v>
+        <v>121643705</v>
       </c>
       <c r="B8" t="n">
-        <v>90742</v>
+        <v>78629</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,14 +1388,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>11, Dlr</t>
+          <t>Ol-Larsbo, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530662</v>
+        <v>530609</v>
       </c>
       <c r="R8" t="n">
-        <v>6739074</v>
+        <v>6739158</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1443,22 +1443,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linn Grejs, Cecilia Rastad, Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Cecilia Rastad, Linn Grejs</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121643705</v>
+        <v>121645997</v>
       </c>
       <c r="B9" t="n">
-        <v>78629</v>
+        <v>90742</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,14 +1494,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ol-Larsbo, Dlr</t>
+          <t>11, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530609</v>
+        <v>530662</v>
       </c>
       <c r="R9" t="n">
-        <v>6739158</v>
+        <v>6739074</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1549,12 +1549,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Cecilia Rastad, Linn Grejs</t>
+          <t>Linn Grejs, Cecilia Rastad, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 64892-2023 artfynd.xlsx
+++ b/artfynd/A 64892-2023 artfynd.xlsx
@@ -2545,10 +2545,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121541039</v>
+        <v>121633817</v>
       </c>
       <c r="B19" t="n">
-        <v>90742</v>
+        <v>78629</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2561,40 +2561,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>8, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>530628</v>
+        <v>530605</v>
       </c>
       <c r="R19" t="n">
-        <v>6739034</v>
+        <v>6739161</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2618,12 +2615,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2632,29 +2639,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121633817</v>
+        <v>121541039</v>
       </c>
       <c r="B20" t="n">
-        <v>78629</v>
+        <v>90742</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2667,37 +2673,40 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>8, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530605</v>
+        <v>530628</v>
       </c>
       <c r="R20" t="n">
-        <v>6739161</v>
+        <v>6739034</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2721,22 +2730,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:27</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:27</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2745,18 +2744,19 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 64892-2023 artfynd.xlsx
+++ b/artfynd/A 64892-2023 artfynd.xlsx
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121635669</v>
+        <v>121643705</v>
       </c>
       <c r="B5" t="n">
-        <v>57365</v>
+        <v>78631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,45 +1019,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>Ol-Larsbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530668</v>
+        <v>530609</v>
       </c>
       <c r="R5" t="n">
-        <v>6739052</v>
+        <v>6739158</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,49 +1079,40 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Cecilia Rastad, Linn Grejs</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121645979</v>
+        <v>121635412</v>
       </c>
       <c r="B6" t="n">
-        <v>90742</v>
+        <v>57365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,40 +1125,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>10, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530657</v>
+        <v>530656</v>
       </c>
       <c r="R6" t="n">
-        <v>6739025</v>
+        <v>6739100</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,40 +1190,49 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linn Grejs, Cecilia Rastad, Lars-Erik Nilsson</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121635412</v>
+        <v>121645979</v>
       </c>
       <c r="B7" t="n">
-        <v>57365</v>
+        <v>90744</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,45 +1245,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>10, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530656</v>
+        <v>530657</v>
       </c>
       <c r="R7" t="n">
-        <v>6739100</v>
+        <v>6739025</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,49 +1305,40 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs, Cecilia Rastad, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121643705</v>
+        <v>121635669</v>
       </c>
       <c r="B8" t="n">
-        <v>78629</v>
+        <v>57365</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,40 +1351,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ol-Larsbo, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530609</v>
+        <v>530668</v>
       </c>
       <c r="R8" t="n">
-        <v>6739158</v>
+        <v>6739052</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1425,30 +1416,39 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Cecilia Rastad, Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1458,7 +1458,7 @@
         <v>121645997</v>
       </c>
       <c r="B9" t="n">
-        <v>90742</v>
+        <v>90744</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121540996</v>
+        <v>121631634</v>
       </c>
       <c r="B10" t="n">
-        <v>91182</v>
+        <v>8436</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,44 +1573,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>7, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530649</v>
+        <v>530482</v>
       </c>
       <c r="R10" t="n">
-        <v>6739106</v>
+        <v>6739197</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1634,12 +1631,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,29 +1655,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121631713</v>
+        <v>121647286</v>
       </c>
       <c r="B11" t="n">
-        <v>78629</v>
+        <v>78631</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1701,16 +1707,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>Fjällgrycksån,, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530489</v>
+        <v>530655</v>
       </c>
       <c r="R11" t="n">
-        <v>6739205</v>
+        <v>6739083</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1742,7 +1751,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1752,7 +1761,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,6 +1770,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1772,7 +1782,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Cecilia Rastad, Lars-Erik Nilsson, Linn Grejs</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1782,7 +1792,7 @@
         <v>121632008</v>
       </c>
       <c r="B12" t="n">
-        <v>78629</v>
+        <v>78631</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2103,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121632920</v>
+        <v>121656060</v>
       </c>
       <c r="B15" t="n">
-        <v>78629</v>
+        <v>57381</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2119,37 +2129,41 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>14, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530531</v>
+        <v>530597</v>
       </c>
       <c r="R15" t="n">
-        <v>6739254</v>
+        <v>6739160</v>
       </c>
       <c r="S15" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2176,19 +2190,9 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,22 +2207,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121632076</v>
+        <v>121632920</v>
       </c>
       <c r="B16" t="n">
-        <v>8436</v>
+        <v>78631</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2227,25 +2231,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2255,13 +2259,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>530487</v>
+        <v>530531</v>
       </c>
       <c r="R16" t="n">
-        <v>6739191</v>
+        <v>6739254</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2290,7 +2294,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2300,7 +2304,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2327,10 +2331,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121632944</v>
+        <v>121633302</v>
       </c>
       <c r="B17" t="n">
-        <v>78629</v>
+        <v>78631</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2367,10 +2371,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>530510</v>
+        <v>530588</v>
       </c>
       <c r="R17" t="n">
-        <v>6739257</v>
+        <v>6739210</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2402,7 +2406,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2412,7 +2416,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2439,10 +2443,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121656060</v>
+        <v>121632076</v>
       </c>
       <c r="B18" t="n">
-        <v>57381</v>
+        <v>8436</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2451,45 +2455,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>14, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>530597</v>
+        <v>530487</v>
       </c>
       <c r="R18" t="n">
-        <v>6739160</v>
+        <v>6739191</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2516,9 +2516,19 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2533,22 +2543,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121633817</v>
+        <v>121541052</v>
       </c>
       <c r="B19" t="n">
-        <v>78629</v>
+        <v>56569</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2561,37 +2571,57 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>9, Fjällgrycken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>530605</v>
+        <v>530653</v>
       </c>
       <c r="R19" t="n">
-        <v>6739161</v>
+        <v>6739025</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2615,22 +2645,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:27</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:27</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2645,22 +2665,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121541039</v>
+        <v>121633817</v>
       </c>
       <c r="B20" t="n">
-        <v>90742</v>
+        <v>78631</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2673,40 +2693,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>8, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530628</v>
+        <v>530605</v>
       </c>
       <c r="R20" t="n">
-        <v>6739034</v>
+        <v>6739161</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2730,12 +2747,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2744,29 +2771,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121631841</v>
+        <v>121541039</v>
       </c>
       <c r="B21" t="n">
-        <v>78629</v>
+        <v>90744</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2779,37 +2805,40 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>8, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530484</v>
+        <v>530628</v>
       </c>
       <c r="R21" t="n">
-        <v>6739192</v>
+        <v>6739034</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2833,22 +2862,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:12</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:12</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2857,28 +2876,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121633302</v>
+        <v>121631841</v>
       </c>
       <c r="B22" t="n">
-        <v>78629</v>
+        <v>78631</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2915,10 +2935,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530588</v>
+        <v>530484</v>
       </c>
       <c r="R22" t="n">
-        <v>6739210</v>
+        <v>6739192</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2950,7 +2970,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2960,7 +2980,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2987,10 +3007,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121647286</v>
+        <v>121632944</v>
       </c>
       <c r="B23" t="n">
-        <v>78629</v>
+        <v>78631</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3021,19 +3041,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Fjällgrycksån,, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>530655</v>
+        <v>530510</v>
       </c>
       <c r="R23" t="n">
-        <v>6739083</v>
+        <v>6739257</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3065,7 +3082,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3075,7 +3092,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3084,7 +3101,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3096,17 +3112,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lars-Erik Nilsson, Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121631634</v>
+        <v>121631713</v>
       </c>
       <c r="B24" t="n">
-        <v>8436</v>
+        <v>78631</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3115,25 +3131,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3143,10 +3159,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530482</v>
+        <v>530489</v>
       </c>
       <c r="R24" t="n">
-        <v>6739197</v>
+        <v>6739205</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3178,7 +3194,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3188,7 +3204,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3215,10 +3231,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121541052</v>
+        <v>121540996</v>
       </c>
       <c r="B25" t="n">
-        <v>56569</v>
+        <v>91184</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3227,58 +3243,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>9, Fjällgrycken, Dlr</t>
+          <t>7, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>530653</v>
+        <v>530649</v>
       </c>
       <c r="R25" t="n">
-        <v>6739025</v>
+        <v>6739106</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3319,6 +3318,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64892-2023 artfynd.xlsx
+++ b/artfynd/A 64892-2023 artfynd.xlsx
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121643705</v>
+        <v>121635412</v>
       </c>
       <c r="B5" t="n">
-        <v>78631</v>
+        <v>57365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,40 +1019,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ol-Larsbo, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530609</v>
+        <v>530656</v>
       </c>
       <c r="R5" t="n">
-        <v>6739158</v>
+        <v>6739100</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,40 +1084,49 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Cecilia Rastad, Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121635412</v>
+        <v>121645997</v>
       </c>
       <c r="B6" t="n">
-        <v>57365</v>
+        <v>90745</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,45 +1139,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>11, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530656</v>
+        <v>530662</v>
       </c>
       <c r="R6" t="n">
-        <v>6739100</v>
+        <v>6739074</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,49 +1199,40 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Cecilia Rastad, Linn Grejs</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121645979</v>
+        <v>121643705</v>
       </c>
       <c r="B7" t="n">
-        <v>90744</v>
+        <v>78632</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,21 +1245,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1268,14 +1268,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>10, Dlr</t>
+          <t>Ol-Larsbo, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530657</v>
+        <v>530609</v>
       </c>
       <c r="R7" t="n">
-        <v>6739025</v>
+        <v>6739158</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1323,22 +1323,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linn Grejs, Cecilia Rastad, Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Cecilia Rastad, Linn Grejs</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121635669</v>
+        <v>121645979</v>
       </c>
       <c r="B8" t="n">
-        <v>57365</v>
+        <v>90745</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1351,45 +1351,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>10, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530668</v>
+        <v>530657</v>
       </c>
       <c r="R8" t="n">
-        <v>6739052</v>
+        <v>6739025</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1416,49 +1411,40 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Cecilia Rastad, Linn Grejs</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121645997</v>
+        <v>121635669</v>
       </c>
       <c r="B9" t="n">
-        <v>90744</v>
+        <v>57365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,40 +1457,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>11, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530662</v>
+        <v>530668</v>
       </c>
       <c r="R9" t="n">
-        <v>6739074</v>
+        <v>6739052</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1531,40 +1522,49 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linn Grejs, Cecilia Rastad, Lars-Erik Nilsson</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121631634</v>
+        <v>121541052</v>
       </c>
       <c r="B10" t="n">
-        <v>8436</v>
+        <v>56569</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,41 +1573,61 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>9, Fjällgrycken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530482</v>
+        <v>530653</v>
       </c>
       <c r="R10" t="n">
-        <v>6739197</v>
+        <v>6739025</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,22 +1651,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:02</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:02</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1661,22 +1671,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121647286</v>
+        <v>121656060</v>
       </c>
       <c r="B11" t="n">
-        <v>78631</v>
+        <v>57381</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1689,40 +1699,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fjällgrycksån,, Dlr</t>
+          <t>14, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530655</v>
+        <v>530597</v>
       </c>
       <c r="R11" t="n">
-        <v>6739083</v>
+        <v>6739160</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1749,50 +1760,39 @@
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lars-Erik Nilsson, Linn Grejs</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121632008</v>
+        <v>121631841</v>
       </c>
       <c r="B12" t="n">
-        <v>78631</v>
+        <v>78632</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>530493</v>
+        <v>530484</v>
       </c>
       <c r="R12" t="n">
-        <v>6739190</v>
+        <v>6739192</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1901,10 +1901,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121656049</v>
+        <v>121631713</v>
       </c>
       <c r="B13" t="n">
-        <v>57381</v>
+        <v>78632</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1917,41 +1917,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>13, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530570</v>
+        <v>530489</v>
       </c>
       <c r="R13" t="n">
-        <v>6739299</v>
+        <v>6739205</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1978,9 +1974,19 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1995,22 +2001,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121656035</v>
+        <v>121632008</v>
       </c>
       <c r="B14" t="n">
-        <v>57381</v>
+        <v>78632</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2023,41 +2029,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>12, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>530558</v>
+        <v>530493</v>
       </c>
       <c r="R14" t="n">
-        <v>6739302</v>
+        <v>6739190</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,9 +2086,19 @@
           <t>2024-12-17</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2101,22 +2113,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121656060</v>
+        <v>121540996</v>
       </c>
       <c r="B15" t="n">
-        <v>57381</v>
+        <v>91185</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2125,45 +2137,44 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>14, Dlr</t>
+          <t>7, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>530597</v>
+        <v>530649</v>
       </c>
       <c r="R15" t="n">
-        <v>6739160</v>
+        <v>6739106</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2187,12 +2198,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2201,6 +2212,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2222,7 +2234,7 @@
         <v>121632920</v>
       </c>
       <c r="B16" t="n">
-        <v>78631</v>
+        <v>78632</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2334,7 +2346,7 @@
         <v>121633302</v>
       </c>
       <c r="B17" t="n">
-        <v>78631</v>
+        <v>78632</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2443,10 +2455,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121632076</v>
+        <v>121633817</v>
       </c>
       <c r="B18" t="n">
-        <v>8436</v>
+        <v>78632</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2455,25 +2467,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2483,10 +2495,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>530487</v>
+        <v>530605</v>
       </c>
       <c r="R18" t="n">
-        <v>6739191</v>
+        <v>6739161</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2518,7 +2530,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2528,7 +2540,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2555,10 +2567,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121541052</v>
+        <v>121656049</v>
       </c>
       <c r="B19" t="n">
-        <v>56569</v>
+        <v>57381</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2571,16 +2583,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2588,40 +2600,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>9, Fjällgrycken, Dlr</t>
+          <t>13, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>530653</v>
+        <v>530570</v>
       </c>
       <c r="R19" t="n">
-        <v>6739025</v>
+        <v>6739299</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2645,12 +2641,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2677,10 +2673,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121633817</v>
+        <v>121647286</v>
       </c>
       <c r="B20" t="n">
-        <v>78631</v>
+        <v>78632</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2711,16 +2707,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>Fjällgrycksån,, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530605</v>
+        <v>530655</v>
       </c>
       <c r="R20" t="n">
-        <v>6739161</v>
+        <v>6739083</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2752,7 +2751,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2762,7 +2761,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2771,6 +2770,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2782,17 +2782,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Cecilia Rastad, Lars-Erik Nilsson, Linn Grejs</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121541039</v>
+        <v>121631634</v>
       </c>
       <c r="B21" t="n">
-        <v>90744</v>
+        <v>8436</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2801,44 +2801,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>8, Dlr</t>
+          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530628</v>
+        <v>530482</v>
       </c>
       <c r="R21" t="n">
-        <v>6739034</v>
+        <v>6739197</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2862,12 +2859,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2876,29 +2883,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linn Grejs</t>
+          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121631841</v>
+        <v>121632076</v>
       </c>
       <c r="B22" t="n">
-        <v>78631</v>
+        <v>8436</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2907,25 +2913,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2935,10 +2941,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530484</v>
+        <v>530487</v>
       </c>
       <c r="R22" t="n">
-        <v>6739192</v>
+        <v>6739191</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2970,7 +2976,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2980,7 +2986,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3010,7 +3016,7 @@
         <v>121632944</v>
       </c>
       <c r="B23" t="n">
-        <v>78631</v>
+        <v>78632</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3119,10 +3125,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121631713</v>
+        <v>121541039</v>
       </c>
       <c r="B24" t="n">
-        <v>78631</v>
+        <v>90745</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3135,37 +3141,40 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Fjällgrycksån, Fjällgrycksån, Dlr</t>
+          <t>8, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>530489</v>
+        <v>530628</v>
       </c>
       <c r="R24" t="n">
-        <v>6739205</v>
+        <v>6739034</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3189,22 +3198,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:08</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:08</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3213,28 +3212,29 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Linn Grejs, Lars-Erik Nilsson</t>
+          <t>Linn Grejs</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121540996</v>
+        <v>121656035</v>
       </c>
       <c r="B25" t="n">
-        <v>91184</v>
+        <v>57381</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3243,44 +3243,45 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>7, Dlr</t>
+          <t>12, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>530649</v>
+        <v>530558</v>
       </c>
       <c r="R25" t="n">
-        <v>6739106</v>
+        <v>6739302</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3304,12 +3305,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3318,7 +3319,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64892-2023 artfynd.xlsx
+++ b/artfynd/A 64892-2023 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>121635412</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>121635669</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
